--- a/tests/fixtures/import/tc70-aero-hpt-blade-thermal-gaps.xlsx
+++ b/tests/fixtures/import/tc70-aero-hpt-blade-thermal-gaps.xlsx
@@ -861,7 +861,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semi-quantitative thermal paint bands (±25K)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1185,6 +1190,11 @@
       <c r="D9" t="n">
         <v>2</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Experienced analyst with standard workflow</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Experienced analyst, standard workflow</t>
@@ -1279,6 +1289,11 @@
       <c r="D12" t="n">
         <v>2</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Adequate spatial resolution for exit plane</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>48-point rake provides adequate spatial resolution</t>
@@ -1307,6 +1322,11 @@
       <c r="D13" t="n">
         <v>3</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Engine-representative conditions required</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Engine-representative Reynolds and Mach numbers</t>
@@ -1335,6 +1355,11 @@
       <c r="D14" t="n">
         <v>2</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Geometric fidelity within 0.5mm</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Cascade rig geometry matches engine within 0.5mm</t>
@@ -1396,6 +1421,11 @@
       <c r="D16" t="n">
         <v>2</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Peak surface temperature is primary QoI</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Peak surface temperature is the primary QoI</t>
@@ -1424,6 +1454,11 @@
       <c r="D17" t="n">
         <v>2</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cascade conditions representative of take-off</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Cascade rig conditions representative of take-off</t>
@@ -1452,6 +1487,11 @@
       <c r="D18" t="n">
         <v>3</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ISO 17025 traceable pedigree required</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>All input data from ISO 17025 calibrated instruments with traceable pedigree</t>
@@ -1480,6 +1520,11 @@
       <c r="D19" t="n">
         <v>3</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quarterly independent review required</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Independent review board conducted quarterly review</t>
@@ -1508,6 +1553,11 @@
       <c r="D20" t="n">
         <v>2</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CM via version control required</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Configuration management via Git + ANSYS Workbench project archive</t>
@@ -1556,6 +1606,11 @@
       <c r="D22" t="n">
         <v>2</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sensitivity within 2% required</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Sensitivity study on inlet turbulence intensity (±20%) shows &lt;1.5% variation in peak T</t>
@@ -1583,6 +1638,11 @@
       </c>
       <c r="D23" t="n">
         <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prior use in 3+ engine variants</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1646,12 +1706,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Not accepted</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Model shows promise for screening-level predictions but three gaps prevent acceptance for detailed design use at MRL 3: (1) Discretization error at blade tip is unresolved — 12% mesh sensitivity in the critical tip gap region; (2) Results uncertainty factor is unassessed — no probabilistic UQ on peak temperature prediction despite being required at MRL 3; (3) Thermal paint validation lacks uncertainty quantification — semi-quantitative nature (±25K bands) not formally characterized. Recommend: complete tip region mesh refinement study, perform Monte Carlo UQ on peak temperature, and quantify thermal paint comparison uncertainty before re-assessment.</t>
+          <t>Board accepts model for screening-level use despite known gaps. Discretization error at blade tip (achieved=1 vs required=3) accepted with condition that tip region study is completed before PDR. Results uncertainty not yet assessed — to be addressed in next cycle. Mesh convergence self-study has no external comparator.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">

--- a/tests/fixtures/import/tc70-aero-hpt-blade-thermal-gaps.xlsx
+++ b/tests/fixtures/import/tc70-aero-hpt-blade-thermal-gaps.xlsx
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,6 +1019,11 @@
           <t>Factor Status</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linked Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1056,6 +1061,11 @@
           <t>(status)</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(URI)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1169,7 +1179,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>not-assessed</t>
+          <t>scoped-out</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1395,7 +1405,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mean error 1.8% passes; max 4.2% at endwall slightly exceeds 3% target but acceptable for preliminary design screening</t>
+          <t>Mean error 1.8% passes; max 4.2% at endwall within tolerance for screening</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1535,6 +1545,11 @@
           <t>assessed</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://aeroeng.example.org/validation/review-2026-q1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1568,6 +1583,11 @@
           <t>assessed</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://aeroeng.example.org/validation/review-2026-q1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1583,6 +1603,11 @@
       <c r="C21" t="n">
         <v>3</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Probabilistic UQ on peak temperature prediction required at MRL 3</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>not-assessed</t>
@@ -1619,6 +1644,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>assessed</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://aeroeng.example.org/validation/cascade-temp-comparison</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1741,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Board accepts model for screening-level use despite known gaps. Discretization error at blade tip (achieved=1 vs required=3) accepted with condition that tip region study is completed before PDR. Results uncertainty not yet assessed — to be addressed in next cycle. Mesh convergence self-study has no external comparator.</t>
+          <t>Accepted for preliminary screening use at MRL 3. Board acknowledges three known gaps requiring resolution before detailed design phase: (1) Discretization error at blade tip is unresolved — 12% mesh sensitivity in the critical tip gap region, achieved level 1 vs required level 3; (2) Results uncertainty factor is unassessed — no probabilistic UQ on peak temperature prediction despite being required at MRL 3; (3) Mesh convergence study is a self-convergence check with no independent comparator dataset. Board accepted based on screening-level risk tolerance with mandatory re-assessment before CDR.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
